--- a/SHGraduationWarning/Template/課程與課規比對樣板.xlsx
+++ b/SHGraduationWarning/Template/課程與課規比對樣板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ischoolProject\ScoreReportDAL\SHGraduationWarning\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4949AB52-A7DB-4600-BB62-463632ABAFDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA113F6-FC5E-464F-821F-5FB9AE6C735F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="2460" windowWidth="21600" windowHeight="11295" xr2:uid="{17DE5928-7095-4D16-BD4A-1063628BFD2C}"/>
+    <workbookView xWindow="5790" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{17DE5928-7095-4D16-BD4A-1063628BFD2C}"/>
   </bookViews>
   <sheets>
     <sheet name="依課程為主比對課規不符合" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
   <si>
     <t>課程系統編號</t>
   </si>
@@ -87,30 +87,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>新科目名稱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>新</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>科目級別</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>使用課程規劃表</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -127,7 +103,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -154,11 +130,6 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -182,7 +153,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -191,9 +162,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -213,9 +181,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -253,7 +221,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -359,7 +327,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -501,7 +469,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -509,16 +477,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A0B7FED-4591-494C-A0F3-C5E31ABC4EFE}">
-  <dimension ref="A1:O1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,16 +518,10 @@
       <c r="K1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>13</v>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -574,21 +534,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC761B58-D9A2-4C60-A8F8-110BCF4D76CB}">
   <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>

--- a/SHGraduationWarning/Template/課程與課規比對樣板.xlsx
+++ b/SHGraduationWarning/Template/課程與課規比對樣板.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ischoolProject\ScoreReportDAL\SHGraduationWarning\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA113F6-FC5E-464F-821F-5FB9AE6C735F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C86B18-BA58-4CD2-9361-E161D4187E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5790" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{17DE5928-7095-4D16-BD4A-1063628BFD2C}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21585" windowHeight="11295" xr2:uid="{17DE5928-7095-4D16-BD4A-1063628BFD2C}"/>
   </bookViews>
   <sheets>
-    <sheet name="依課程為主比對課規不符合" sheetId="1" r:id="rId1"/>
-    <sheet name="依課規為主比對課程不符合" sheetId="2" r:id="rId2"/>
+    <sheet name="開課課程比對" sheetId="1" r:id="rId1"/>
+    <sheet name="課程規劃比對" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
